--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27260" windowHeight="11920"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
+    <sheet name="主要构造物水文条件" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -42,10 +42,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -68,6 +68,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -75,8 +90,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -84,20 +115,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -111,41 +128,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,54 +159,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,187 +234,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,8 +446,58 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -482,211 +532,161 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27260" windowHeight="11920"/>
+    <workbookView windowWidth="27260" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="主要构造物水文条件" sheetId="1" r:id="rId1"/>
@@ -43,11 +43,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -63,9 +63,86 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -76,6 +153,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -83,40 +175,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,97 +213,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -234,13 +229,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -258,31 +397,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,127 +409,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,8 +441,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -457,21 +452,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -487,32 +467,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -535,8 +489,49 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -545,148 +540,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -694,10 +689,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1019,8 +1014,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G127"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="16.7211538461538" customWidth="1"/>
     <col min="2" max="2" width="24.2788461538462" customWidth="1"/>
@@ -1029,37 +1024,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="14" customHeight="1" spans="1:7">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
+    <row r="2" s="1" customFormat="1"/>
+    <row r="3" s="1" customFormat="1"/>
+    <row r="4" s="1" customFormat="1"/>
+    <row r="5" s="1" customFormat="1"/>
+    <row r="6" s="1" customFormat="1"/>
+    <row r="7" s="1" customFormat="1"/>
+    <row r="8" s="1" customFormat="1"/>
+    <row r="9" s="1" customFormat="1"/>
+    <row r="10" s="1" customFormat="1"/>
+    <row r="11" s="1" customFormat="1"/>
+    <row r="12" s="1" customFormat="1"/>
+    <row r="13" s="1" customFormat="1"/>
+    <row r="14" s="1" customFormat="1"/>
+    <row r="15" s="1" customFormat="1"/>
+    <row r="16" s="1" customFormat="1"/>
+    <row r="17" s="1" customFormat="1"/>
+    <row r="18" s="1" customFormat="1"/>
+    <row r="19" s="1" customFormat="1"/>
+    <row r="20" s="1" customFormat="1"/>
+    <row r="21" s="1" customFormat="1"/>
+    <row r="22" s="1" customFormat="1"/>
+    <row r="23" s="1" customFormat="1"/>
+    <row r="24" s="1" customFormat="1"/>
+    <row r="25" s="1" customFormat="1"/>
+    <row r="26" s="1" customFormat="1"/>
+    <row r="27" s="1" customFormat="1"/>
+    <row r="28" s="1" customFormat="1"/>
+    <row r="29" s="1" customFormat="1"/>
+    <row r="30" s="1" customFormat="1"/>
+    <row r="31" s="1" customFormat="1"/>
+    <row r="32" s="1" customFormat="1"/>
+    <row r="33" s="1" customFormat="1"/>
+    <row r="34" s="1" customFormat="1"/>
+    <row r="35" s="1" customFormat="1"/>
+    <row r="36" s="1" customFormat="1"/>
+    <row r="37" s="1" customFormat="1"/>
+    <row r="38" s="1" customFormat="1"/>
+    <row r="39" s="1" customFormat="1"/>
+    <row r="40" s="1" customFormat="1"/>
+    <row r="41" s="1" customFormat="1"/>
+    <row r="42" s="1" customFormat="1"/>
+    <row r="43" s="1" customFormat="1"/>
+    <row r="44" s="1" customFormat="1"/>
+    <row r="45" s="1" customFormat="1"/>
+    <row r="46" s="1" customFormat="1"/>
+    <row r="47" s="1" customFormat="1"/>
+    <row r="48" s="1" customFormat="1"/>
+    <row r="49" s="1" customFormat="1"/>
+    <row r="50" s="1" customFormat="1"/>
+    <row r="51" s="1" customFormat="1"/>
+    <row r="52" s="1" customFormat="1"/>
+    <row r="53" s="1" customFormat="1"/>
+    <row r="54" s="1" customFormat="1"/>
+    <row r="55" s="1" customFormat="1"/>
+    <row r="56" s="1" customFormat="1"/>
+    <row r="57" s="1" customFormat="1"/>
+    <row r="58" s="1" customFormat="1"/>
+    <row r="59" s="1" customFormat="1"/>
+    <row r="60" s="1" customFormat="1"/>
+    <row r="61" s="1" customFormat="1"/>
+    <row r="62" s="1" customFormat="1"/>
+    <row r="63" s="1" customFormat="1"/>
+    <row r="64" s="1" customFormat="1"/>
+    <row r="65" s="1" customFormat="1"/>
+    <row r="66" s="1" customFormat="1"/>
+    <row r="67" s="1" customFormat="1"/>
+    <row r="68" s="1" customFormat="1"/>
+    <row r="69" s="1" customFormat="1"/>
+    <row r="70" s="1" customFormat="1"/>
+    <row r="71" s="1" customFormat="1"/>
+    <row r="72" s="1" customFormat="1"/>
+    <row r="73" s="1" customFormat="1"/>
+    <row r="74" s="1" customFormat="1"/>
+    <row r="75" s="1" customFormat="1"/>
+    <row r="76" s="1" customFormat="1"/>
+    <row r="77" s="1" customFormat="1"/>
+    <row r="78" s="1" customFormat="1"/>
+    <row r="79" s="1" customFormat="1"/>
+    <row r="80" s="1" customFormat="1"/>
+    <row r="81" s="1" customFormat="1"/>
+    <row r="82" s="1" customFormat="1"/>
+    <row r="83" s="1" customFormat="1"/>
+    <row r="84" s="1" customFormat="1"/>
+    <row r="85" s="1" customFormat="1"/>
+    <row r="86" s="1" customFormat="1"/>
+    <row r="87" s="1" customFormat="1"/>
+    <row r="88" s="1" customFormat="1"/>
+    <row r="89" s="1" customFormat="1"/>
+    <row r="90" s="1" customFormat="1"/>
+    <row r="91" s="1" customFormat="1"/>
+    <row r="92" s="1" customFormat="1"/>
+    <row r="93" s="1" customFormat="1"/>
+    <row r="94" s="1" customFormat="1"/>
+    <row r="95" s="1" customFormat="1"/>
+    <row r="96" s="1" customFormat="1"/>
+    <row r="97" s="1" customFormat="1"/>
+    <row r="98" s="1" customFormat="1"/>
+    <row r="99" s="1" customFormat="1"/>
+    <row r="100" s="1" customFormat="1"/>
+    <row r="101" s="1" customFormat="1"/>
+    <row r="102" s="1" customFormat="1"/>
+    <row r="103" s="1" customFormat="1"/>
+    <row r="104" s="1" customFormat="1"/>
+    <row r="105" s="1" customFormat="1"/>
+    <row r="106" s="1" customFormat="1"/>
+    <row r="107" s="1" customFormat="1"/>
+    <row r="108" s="1" customFormat="1"/>
+    <row r="109" s="1" customFormat="1"/>
+    <row r="110" s="1" customFormat="1"/>
+    <row r="111" s="1" customFormat="1"/>
+    <row r="112" s="1" customFormat="1"/>
+    <row r="113" s="1" customFormat="1"/>
+    <row r="114" s="1" customFormat="1"/>
+    <row r="115" s="1" customFormat="1"/>
+    <row r="116" s="1" customFormat="1"/>
+    <row r="117" s="1" customFormat="1"/>
+    <row r="118" s="1" customFormat="1"/>
+    <row r="119" s="1" customFormat="1"/>
+    <row r="120" s="1" customFormat="1"/>
+    <row r="121" s="1" customFormat="1"/>
+    <row r="122" s="1" customFormat="1"/>
+    <row r="123" s="1" customFormat="1"/>
+    <row r="124" s="1" customFormat="1"/>
+    <row r="125" s="1" customFormat="1"/>
+    <row r="126" s="1" customFormat="1"/>
+    <row r="127" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="主要构造物水文条件" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -42,9 +42,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -71,27 +71,19 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -100,17 +92,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -131,15 +114,40 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -155,6 +163,44 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -162,55 +208,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -229,49 +229,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -283,133 +403,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,11 +447,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -472,30 +502,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -510,21 +516,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -535,150 +526,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1173,6 +1173,11 @@
     <row r="126" s="1" customFormat="1"/>
     <row r="127" s="1" customFormat="1"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数字格式错误！" sqref="B$1:C$1048576">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importMainStructureHydrology.xlsx
@@ -42,10 +42,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -64,36 +64,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -107,7 +78,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -129,6 +108,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -145,9 +132,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,9 +147,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -171,14 +179,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,29 +209,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,13 +229,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,43 +373,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -301,115 +397,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,15 +438,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -462,11 +453,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -486,32 +516,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -526,162 +535,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1174,9 +1174,7 @@
     <row r="127" s="1" customFormat="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数字格式错误！" sqref="B$1:C$1048576">
-      <formula1>0</formula1>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数字格式错误！" sqref="B$1:C$1048576"/>
   </dataValidations>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
